--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1015,7 +1015,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8863,7 +8863,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11721,7 +11721,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12133,7 +12133,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14749,7 +14749,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17607,7 +17607,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -18019,7 +18019,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18673,7 +18673,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18915,7 +18915,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19981,7 +19981,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20223,7 +20223,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>89</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.02549883938164753</v>
       </c>
@@ -1422,9 +1419,6 @@
       <c r="P5" t="n">
         <v>488</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.139813860879146</v>
       </c>
@@ -2076,9 +2070,6 @@
       <c r="P8" t="n">
         <v>529</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1515605172235005</v>
       </c>
@@ -2730,9 +2721,6 @@
       <c r="P11" t="n">
         <v>515</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.1475494638376234</v>
       </c>
@@ -3384,9 +3372,6 @@
       <c r="P14" t="n">
         <v>487</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.1395273570658691</v>
       </c>
@@ -4038,9 +4023,6 @@
       <c r="P17" t="n">
         <v>643</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.1842219519370715</v>
       </c>
@@ -4692,9 +4674,6 @@
       <c r="P20" t="n">
         <v>549</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1572905934890393</v>
       </c>
@@ -5346,9 +5325,6 @@
       <c r="P23" t="n">
         <v>570</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.163307173567855</v>
       </c>
@@ -6000,9 +5976,6 @@
       <c r="P26" t="n">
         <v>542</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.1552850667961007</v>
       </c>
@@ -6654,9 +6627,6 @@
       <c r="P29" t="n">
         <v>513</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1469764562110694</v>
       </c>
@@ -7308,9 +7278,6 @@
       <c r="P32" t="n">
         <v>458</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.1312187464808379</v>
       </c>
@@ -7962,9 +7929,6 @@
       <c r="P35" t="n">
         <v>532</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1524200286633313</v>
       </c>
@@ -8616,9 +8580,6 @@
       <c r="P38" t="n">
         <v>580</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1661722117006244</v>
       </c>
@@ -9270,9 +9231,6 @@
       <c r="P41" t="n">
         <v>522</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1495549905305619</v>
       </c>
@@ -9924,9 +9882,6 @@
       <c r="P44" t="n">
         <v>550</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1575770973023162</v>
       </c>
@@ -10578,9 +10533,6 @@
       <c r="P47" t="n">
         <v>531</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1521335248500544</v>
       </c>
@@ -11232,9 +11184,6 @@
       <c r="P50" t="n">
         <v>689</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1974011273478107</v>
       </c>
@@ -11886,9 +11835,6 @@
       <c r="P53" t="n">
         <v>612</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.1753403337254864</v>
       </c>
@@ -12540,9 +12486,6 @@
       <c r="P56" t="n">
         <v>533</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.1527065324766082</v>
       </c>
@@ -13194,9 +13137,6 @@
       <c r="P59" t="n">
         <v>619</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.177345860418425</v>
       </c>
@@ -13848,9 +13788,6 @@
       <c r="P62" t="n">
         <v>324</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.09282723550172808</v>
       </c>
@@ -14502,9 +14439,6 @@
       <c r="P65" t="n">
         <v>428</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1226236320825297</v>
       </c>
@@ -15156,9 +15090,6 @@
       <c r="P68" t="n">
         <v>570</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.163307173567855</v>
       </c>
@@ -15810,9 +15741,6 @@
       <c r="P71" t="n">
         <v>541</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.1549985629828237</v>
       </c>
@@ -16464,9 +16392,6 @@
       <c r="P74" t="n">
         <v>469</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1343702884268842</v>
       </c>
@@ -17118,9 +17043,6 @@
       <c r="P77" t="n">
         <v>507</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1452574333314078</v>
       </c>
@@ -17772,9 +17694,6 @@
       <c r="P80" t="n">
         <v>434</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.1243426549621913</v>
       </c>
@@ -18426,9 +18345,6 @@
       <c r="P83" t="n">
         <v>400</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.1146015253107754</v>
       </c>
@@ -19080,9 +18996,6 @@
       <c r="P86" t="n">
         <v>545</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.1561445782359315</v>
       </c>
@@ -19734,9 +19647,6 @@
       <c r="P89" t="n">
         <v>489</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.140100364692423</v>
       </c>
@@ -20388,9 +20298,6 @@
       <c r="P92" t="n">
         <v>545</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.1561445782359315</v>
       </c>
@@ -20962,6 +20869,657 @@
         </is>
       </c>
       <c r="BC94" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>496</v>
+      </c>
+      <c r="O95" t="n">
+        <v>496</v>
+      </c>
+      <c r="P95" t="n">
+        <v>496</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.1421058913853615</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>496</v>
+      </c>
+      <c r="O96" t="n">
+        <v>496</v>
+      </c>
+      <c r="P96" t="n">
+        <v>496</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>815</v>
+      </c>
+      <c r="O97" t="n">
+        <v>815</v>
+      </c>
+      <c r="P97" t="n">
+        <v>815</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -21000,7 +21558,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -21083,7 +21641,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -21093,7 +21651,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -21113,7 +21671,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -21145,7 +21703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15803</v>
+        <v>16299</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -21525,6 +21525,657 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>440</v>
+      </c>
+      <c r="O98" t="n">
+        <v>440</v>
+      </c>
+      <c r="P98" t="n">
+        <v>440</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.126061677841853</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>440</v>
+      </c>
+      <c r="O99" t="n">
+        <v>440</v>
+      </c>
+      <c r="P99" t="n">
+        <v>440</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>913</v>
+      </c>
+      <c r="O100" t="n">
+        <v>913</v>
+      </c>
+      <c r="P100" t="n">
+        <v>913</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21558,7 +22209,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -21641,7 +22292,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -21651,7 +22302,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -21671,7 +22322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -21703,7 +22354,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16299</v>
+        <v>16739</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22171,6 +22171,657 @@
         </is>
       </c>
       <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>527</v>
+      </c>
+      <c r="O101" t="n">
+        <v>527</v>
+      </c>
+      <c r="P101" t="n">
+        <v>527</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.1509875095969466</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>527</v>
+      </c>
+      <c r="O102" t="n">
+        <v>527</v>
+      </c>
+      <c r="P102" t="n">
+        <v>527</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>1007</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1007</v>
+      </c>
+      <c r="P103" t="n">
+        <v>1007</v>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG103" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH103" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ103" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -22209,7 +22860,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -22292,7 +22943,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -22302,7 +22953,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -22322,7 +22973,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -22354,7 +23005,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16739</v>
+        <v>17266</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">

--- a/diseases/d211/2026-2029.xlsx
+++ b/diseases/d211/2026-2029.xlsx
@@ -22827,6 +22827,657 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>443</v>
+      </c>
+      <c r="O104" t="n">
+        <v>443</v>
+      </c>
+      <c r="P104" t="n">
+        <v>443</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.1269211892816838</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>443</v>
+      </c>
+      <c r="O105" t="n">
+        <v>443</v>
+      </c>
+      <c r="P105" t="n">
+        <v>443</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis C component.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-c</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D211</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis C</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>慢性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>860</v>
+      </c>
+      <c r="O106" t="n">
+        <v>860</v>
+      </c>
+      <c r="P106" t="n">
+        <v>860</v>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Hepatitis C, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD106" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG106" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH106" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis C component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_C_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22860,7 +23511,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -22943,7 +23594,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -22953,7 +23604,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
@@ -22973,7 +23624,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -23005,7 +23656,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17266</v>
+        <v>17709</v>
       </c>
     </row>
     <row r="16">
